--- a/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
+++ b/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" r:id="Rbc614758ac474a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="banks" sheetId="2" r:id="Rce4a6d1335a44965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cards" sheetId="3" r:id="R494a1f1fb963484e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="offers" sheetId="4" r:id="R141a17d88f854f6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="offer_cards" sheetId="5" r:id="Rc6e0a2dfcce64c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" r:id="R86f24b06952c4a11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="banks" sheetId="2" r:id="R1cd6fd6d07f34d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cards" sheetId="3" r:id="R66d7c808d5d24157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="offers" sheetId="4" r:id="R866ba0ae7ada48e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="offer_cards" sheetId="5" r:id="R89d753401eb04afe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -932,6 +932,24 @@
         <x:v>官方資料查證：2026-07-26</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>聯邦銀行</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>ubot</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>https://www.ubot.com.tw/</x:v>
+      </x:c>
+      <x:c r="D7"/>
+      <x:c r="E7" t="str">
+        <x:v>聯邦銀行信用卡資料，包含聯邦綠卡。</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>官方資料查證：2026-07-26</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1406,6 +1424,88 @@
       <x:c r="O9" s="18" t="str">
         <x:v>官方資料查證：2026-07-26。卡別年費、卡片等級及發卡組織依實際申辦卡別而異，待逐卡別補充。</x:v>
       </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>台新街口聯名卡</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>taishin-jkopay-card</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>taishin</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>https://web.taishinbank.com.tw/TSB/personal/credit/intro/overview/cg038/card001/</x:v>
+      </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10" t="str">
+        <x:v>街口APP繳費享基本0.15%無上限，當月繳費滿NT$1,000可再享2%街口券</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>台新街口聯名卡（暱稱豬富卡）於2026年可綁定街口支付APP繳費；基本回饋為0.15%街口幣無上限，當月街口APP繳費交易滿NT$1,000，可手動領取2%街口券，每月每人上限20元。</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>常以街口支付APP繳水電、學雜費或稅費，且可達成每月NT$1,000繳費門檻並主動領券者。</x:v>
+      </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+      <x:c r="M10" t="str">
+        <x:v>街口APP繳費基本0.15%無上限
+當月繳費滿NT$1,000可再享2%街口券
+可用街口支付繳學雜費，實際學校依街口支付公告</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>加碼2%自2026-07-01起每月限量55,000名，須在街口APP手動領券
+領券額滿即無法補領；回饋為街口券，非現金
+交易與回饋當下均須在街口支付APP綁定本卡</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>官方資料查證：2026-07-26；卡片等級、發卡組織與年費依實際申辦卡別及台新公告為準。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>聯邦綠卡</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>ubot-green-card</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>ubot</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>https://card.ubot.com.tw/card_apply/?GID=64&amp;IDE=A&amp;openExternalBrowser=1</x:v>
+      </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11" t="str">
+        <x:v>綁定指定生活代扣繳並申辦電子化帳單，水電瓦斯與電信費每月享1%刷卡金、上限NT$100</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>聯邦綠卡可於聯邦銀行2026年生活代扣活動中，綁定水費、電費、電信費、瓦斯費或指定公有路邊停車費自動代扣繳；完成電子化帳單後，生活代扣繳交易每月享1%刷卡金，上限NT$100。</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>有固定水電、瓦斯或電信費帳單，想以信用卡自動代扣繳並已使用電子化帳單者。</x:v>
+      </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11" t="str">
+        <x:v>指定生活代扣繳每月1%刷卡金
+每月上限NT$100</x:v>
+      </x:c>
+      <x:c r="N11" t="str">
+        <x:v>生活代扣繳不是一般消費，不提供卡片原始回饋
+本活動須先完成登錄，且僅限活動指定的水費、電費、電信費、瓦斯費及公有路邊停車費
+Visa金融卡、商務差旅卡、採購卡不適用</x:v>
+      </x:c>
+      <x:c r="O11" t="str">
+        <x:v>官方資料查證：2026-07-26；卡片等級、發卡組織與年費依實際申辦卡別及聯邦公告為準。</x:v>
+      </x:c>
+      <x:c r="P11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2184,6 +2284,356 @@
         <x:v>官方卡片頁查證；本列為主權益，個別方案之通路、回饋上限與支付限制請依台新當期公告。</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="66" hidden="0" customHeight="1">
+      <x:c r="A12" s="18" t="str">
+        <x:v>永豐信用卡指定稅款滿 NT$3,000 分 6 期 0 利率</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="str">
+        <x:v>sinopac-designated-tax-installment-2026h1</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>installment</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>2026-01-01 至 06-30 以 Paytax 或大咖 DACARD 繳牌照稅、房屋稅、地價稅，單筆滿 NT$3,000 登錄享 6 期 0 利率</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="str">
+        <x:v>繳納牌照稅、房屋稅或地價稅，且有分期資金需求的永豐信用卡正卡持卡人。</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="str">
+        <x:v>指定稅款單筆滿 NT$3,000，分 6 期 0 利率</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="str">
+        <x:v>Paytax／大咖 DACARD 繳納，免手續費</x:v>
+      </x:c>
+      <x:c r="H12" s="18" t="str">
+        <x:v>2026-01-01 至 06-30，持永豐信用卡透過 Paytax 繳稅服務網（網路、QR Code 或中華電信語音）或大咖 DACARD APP 繳納牌照稅、房屋稅、地價稅；正卡持卡人完成分期總約簽署並於登錄當月繳納單筆滿 NT$3,000，登錄後可享 6 期 0 利率。指定稅款同時提供免手續費；活動另有符合歷史代繳條件者的 0.2% 刷卡金方案。</x:v>
+      </x:c>
+      <x:c r="I12" s="18" t="str">
+        <x:v>2026-01-01</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="str">
+        <x:v>分期</x:v>
+      </x:c>
+      <x:c r="L12" s="18" t="str">
+        <x:v>6期0利率</x:v>
+      </x:c>
+      <x:c r="M12" s="18"/>
+      <x:c r="N12" s="18" t="str">
+        <x:v>單筆指定稅款滿 NT$3,000，並於登錄當月繳納</x:v>
+      </x:c>
+      <x:c r="O12" s="18" t="str">
+        <x:v>限牌照稅、房屋稅、地價稅；限正卡持卡人於 Paytax（網路、QR Code、中華電信語音）或大咖 DACARD APP 繳納，不含便利商店代收、公務機關臨櫃及第三方支付。須於繳納當月底前簽署消費分期總約並完成活動登錄；分期金額占用永久額度。稅款不列入一般消費，八通卡、公司卡、配銷卡、儲值卡及簽帳金融卡不適用。</x:v>
+      </x:c>
+      <x:c r="P12" s="18" t="str">
+        <x:v>https://bank.sinopac.com/sinopacbt/personal/credit-card/discount/650410355.html</x:v>
+      </x:c>
+      <x:c r="Q12" s="18" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="R12" s="18" t="str">
+        <x:v>繳稅,分期,需登錄,期間限定</x:v>
+      </x:c>
+      <x:c r="S12" s="18" t="str">
+        <x:v>官方活動頁查證。活動已於 2026-06-30 結束，保留為 2026 報稅季可查核資料；後續年度需重新查證。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A13" s="18" t="str">
+        <x:v>永豐信用卡繳學費滿額最高回饋 NT$500</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="str">
+        <x:v>sinopac-tuition-payment-rebate-2026h1</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>cashback</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>2026-01-01 至 06-30 透過 i 繳費或學費通繳學費並登錄，當月每滿 NT$50,000 回饋 NT$50，最高 NT$500</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="str">
+        <x:v>有大額學費支出，並可在繳費當月完成活動登錄的永豐信用卡正卡持卡人。</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="str">
+        <x:v>當月每滿 NT$50,000 回饋 NT$50 刷卡金</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="str">
+        <x:v>每戶每月最高回饋 NT$500 刷卡金</x:v>
+      </x:c>
+      <x:c r="H13" s="18" t="str">
+        <x:v>2026-01-01 至 06-30，透過 i 繳費或聯合信用卡中心學費通平台使用永豐信用卡繳納學費，於繳費當月完成活動登錄後，正附卡合併的當月學費每滿 NT$50,000 回饋 NT$50 刷卡金，每戶每月最高 NT$500；回饋於代繳成功次次月起入帳。另可依單筆分期活動申請 0 利率分期。</x:v>
+      </x:c>
+      <x:c r="I13" s="18" t="str">
+        <x:v>2026-01-01</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="str">
+        <x:v>現金回饋</x:v>
+      </x:c>
+      <x:c r="L13" s="18" t="str">
+        <x:v>每滿NT$50,000回饋NT$50</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="str">
+        <x:v>每戶每月最高NT$500</x:v>
+      </x:c>
+      <x:c r="N13" s="18" t="str">
+        <x:v>繳費當月透過 i 繳費或學費通繳納學費並完成活動登錄</x:v>
+      </x:c>
+      <x:c r="O13" s="18" t="str">
+        <x:v>僅限 i 繳費、聯合信用卡中心學費通平台，其他繳費方式不適用；須在繳費當月完成登錄，逾期不可補登。公司卡、配銷卡、八通卡、儲值卡及簽帳金融卡不適用；學費不列入一般消費。</x:v>
+      </x:c>
+      <x:c r="P13" s="18" t="str">
+        <x:v>https://bank.sinopac.com/sinopacbt/personal/credit-card/discount/650410355.html</x:v>
+      </x:c>
+      <x:c r="Q13" s="18" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="R13" s="18" t="str">
+        <x:v>學費,需登錄,期間限定</x:v>
+      </x:c>
+      <x:c r="S13" s="18" t="str">
+        <x:v>官方活動頁查證。活動已於 2026-06-30 結束，保留為 2026 上半年學費季可查核資料；後續學期需重新查證。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="66" hidden="0" customHeight="1">
+      <x:c r="A14" s="18" t="str">
+        <x:v>永豐信用卡公共事業費自動代扣繳最高 2% 回饋</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="str">
+        <x:v>sinopac-utilities-autopay-2percent-2026h2</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>cashback</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="str">
+        <x:v>2026-08-01 至 10-31 先完成兩項水電瓦斯／電信自扣任務並登錄，代扣繳公共事業費享 2% 回饋，最高 NT$50</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="str">
+        <x:v>可在 2026-07-31 前完成兩項公共事業費自動代扣繳，並願意在 8 月登錄的永豐信用卡正卡持卡人。</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="str">
+        <x:v>水費、電費、瓦斯費、中華電信費等自扣繳可適用</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="str">
+        <x:v>完成任務後代扣繳享 2%，最高 NT$50</x:v>
+      </x:c>
+      <x:c r="H14" s="18" t="str">
+        <x:v>2026-08-01 至 10-31，持永豐信用卡以線上申請、DACARD 大咖 APP、公用事業費代繳約定書或信用卡申請書，申請水費、電費、瓦斯費、公有路邊停車費或中華電信費自動代扣繳。若在 2026-01-01 至 07-31 期間申請任二項且完成自動代扣繳總次數達 4 次，並於 8 月成功登錄，可在活動期間享 2% 刷卡金回饋，最高 NT$50。</x:v>
+      </x:c>
+      <x:c r="I14" s="18" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="str">
+        <x:v>2026-10-31</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="str">
+        <x:v>現金回饋</x:v>
+      </x:c>
+      <x:c r="L14" s="18" t="str">
+        <x:v>2%</x:v>
+      </x:c>
+      <x:c r="M14" s="18" t="str">
+        <x:v>最高NT$50</x:v>
+      </x:c>
+      <x:c r="N14" s="18" t="str">
+        <x:v>2026-07-31 前申請公共事業費任二項，完成自扣總次數達4次，並於8月完成登錄</x:v>
+      </x:c>
+      <x:c r="O14" s="18" t="str">
+        <x:v>限指定申請方式的自動代扣繳，單次透過財金繳費稅平台、全國繳費網或其他繳費平台不適用。限量 5,000 名，8 月 1 日開放登錄；八通卡、公司卡、配銷卡及簽帳金融卡不適用。水電瓦斯及電信費不屬一般消費。</x:v>
+      </x:c>
+      <x:c r="P14" s="18" t="str">
+        <x:v>https://bank.sinopac.com/sinopacbt/personal/credit-card/discount/650410355.html</x:v>
+      </x:c>
+      <x:c r="Q14" s="18" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="R14" s="18" t="str">
+        <x:v>水電瓦斯,電信費,加碼,需登錄,期間限定</x:v>
+      </x:c>
+      <x:c r="S14" s="18" t="str">
+        <x:v>官方活動頁查證；活動尚未開始。首扣優惠（2026-01-01 至 12-31）亦在同頁，惟本列聚焦可量化的 2% 夏日加碼。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>聯邦綠卡指定生活代扣繳每月1%刷卡金</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>ubot-green-card-utilities-autopay-2026h2</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>cashback</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>2026-07-01至12-31完成登錄，以聯邦綠卡綁水電瓦斯或電信費自動代扣繳並申辦電子化帳單，每月享1%刷卡金、上限NT$100</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>有固定水電、瓦斯或電信費帳單，想使用信用卡自動代扣繳並可申辦電子化帳單者。</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>完成活動登錄，並以聯邦綠卡綁定指定生活代扣繳與電子化帳單</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>指定生活代扣繳每月1%刷卡金</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>2026-07-01至12-31，聯邦綠卡持卡人完成活動登錄後，綁定台灣自來水、台北自來水、台電、中華電信、台灣大哥大、遠傳電信、指定瓦斯公司或指定公有路邊停車費等生活代扣繳；申辦電子化帳單，即享每月1%刷卡金，月上限NT$100。</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>2026-12-31</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>現金回饋</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>1%</x:v>
+      </x:c>
+      <x:c r="M15" t="str">
+        <x:v>每月最高NT$100</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>活動期間完成登錄，以聯邦綠卡綁定指定生活代扣繳並申辦電子化帳單</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>生活代扣繳非一般消費，不提供原始卡片回饋；須以聯邦認定交易名稱為準。Visa金融卡、商務差旅卡、採購卡不適用；指定業者與完整條款以官方活動頁為準。</x:v>
+      </x:c>
+      <x:c r="P15" t="str">
+        <x:v>https://activity.ubot.com.tw/aws_act/2026/202607autopay/index.htm</x:v>
+      </x:c>
+      <x:c r="Q15" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="R15" t="str">
+        <x:v>水電瓦斯,電信費,加碼,需登錄,期間限定</x:v>
+      </x:c>
+      <x:c r="S15" t="str">
+        <x:v>官方活動頁查證；僅收錄聯邦綠卡專屬每月1%回饋，不將新申辦首扣贈刷卡金混列。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>台新信用卡繳國內學雜費分期最優3.88%起</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>taishin-tuition-installment-2026h2</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>installment</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>2026-07-10至12-31，刷台新信用卡繳國內學雜費單筆滿NT$1,000，分3／6期利率3.88%起且0手續費</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>需繳國內學雜費並希望以信用卡分期付款的台新信用卡持卡人。</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>單筆學雜費滿NT$1,000</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>分3／6期3.88%、12期5.88%、18／24／30期8.88%，均0手續費</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>2026-07-10至12-31，刷台新信用卡繳納幼稚園、國小、國高中、大專院校、進修推廣、國內美國學校及外僑學校等國內學雜費；單筆滿NT$1,000可享分3／6期3.88%、12期5.88%、18／24／30期8.88%優惠利率，均0手續費。</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>2026-07-10</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>2026-12-31</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>分期</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>3／6期3.88%起、0手續費</x:v>
+      </x:c>
+      <x:c r="M16"/>
+      <x:c r="N16" t="str">
+        <x:v>繳納前至官網登錄；數位通路免登錄。街口支付或悠遊付繳費後，須進線台新客服辦理分期</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>便利商店繳學雜費不適用。活動期間僅須登錄一次，後續每筆可享自動分期；如已設定指定卡片分期，欲參加本活動須進線台新客服。可繳學校與繳費帳號依繳款單及繳費平台公告為準。</x:v>
+      </x:c>
+      <x:c r="P16" t="str">
+        <x:v>https://mkpcard.taishinbank.com.tw/tscccms/promotion/detail/WM_20260617134739441</x:v>
+      </x:c>
+      <x:c r="Q16" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="R16" t="str">
+        <x:v>學費,分期,需登錄,期間限定</x:v>
+      </x:c>
+      <x:c r="S16" t="str">
+        <x:v>官方活動頁查證；全體適用台新信用卡，先連結既有台新Richart卡。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>台新街口聯名卡綁街口APP繳稅費最高2.15%</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>taishin-jkopay-card-bill-payments-2026</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>cashback</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>2026全年綁街口聯名卡於街口APP繳稅費，基本0.15%無上限；當月繳費滿NT$1,000再享2%街口券、每月上限20元</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>使用街口支付APP繳稅費或學雜費，且可每月累積NT$1,000繳費並手動領券的街口聯名卡持卡人。</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>當月街口APP繳費交易滿NT$1,000可取得加碼</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>基本0.15%街口幣無上限，加碼2%街口券</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>2026-01-01至12-31，街口聯名卡綁定街口支付APP繳稅費可享基本0.15%回饋無上限；當月街口APP繳費交易滿NT$1,000，手動領券後可再享2%街口券，每月每人上限20元。官方頁另明載可用街口支付繳學雜費，實際可繳學校依街口支付公告為準。</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>2026-01-01</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>2026-12-31</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>點數回饋</x:v>
+      </x:c>
+      <x:c r="L17" t="str">
+        <x:v>最高2.15%</x:v>
+      </x:c>
+      <x:c r="M17" t="str">
+        <x:v>加碼2%每月每人上限20元街口券；2026-07-01起每月限量55,000名</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>交易與回饋當下均在街口支付APP綁定街口聯名卡；達NT$1,000後至APP手動領取加碼券</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>領券以系統領取時間判定，額滿無法補領；加碼為街口券，可於全台7-ELEVEN折抵，非現金。若取消綁定本卡或註銷街口支付帳號，視同放棄回饋；繳納項目與學校依街口支付公告。</x:v>
+      </x:c>
+      <x:c r="P17" t="str">
+        <x:v>https://www.taishinbank.com.tw/TSB/personal/credit/intro/overview/future/24e1ad87-2cad-11f1-b50f-0050568c09e3</x:v>
+      </x:c>
+      <x:c r="Q17" t="str">
+        <x:v>2026-07-26</x:v>
+      </x:c>
+      <x:c r="R17" t="str">
+        <x:v>繳稅,學費,水電瓦斯,行動支付,加碼,需登錄,期間限定</x:v>
+      </x:c>
+      <x:c r="S17" t="str">
+        <x:v>官方活動頁與台新學雜費活動頁交叉查證；水／電等費用與學雜費均有台新官方頁明載。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
     <x:dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="1" errorTitle="主分類代碼" error="只能填六個分類代碼之一，見「說明」工作表。" sqref="C2:C1000">
@@ -2332,6 +2782,116 @@
         <x:v>台新Richart卡切換刷主權益</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="18" t="str">
+        <x:v>sinopac-designated-tax-installment-2026h1</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="str">
+        <x:v>dawho-cashback-card</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>永豐信用卡活動；DAWHO卡適用，依排除卡別規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="18" t="str">
+        <x:v>sinopac-designated-tax-installment-2026h1</x:v>
+      </x:c>
+      <x:c r="B13" s="18" t="str">
+        <x:v>sinopac-dual-currency-card</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>永豐信用卡活動；幣倍卡適用，依排除卡別規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A14" s="18" t="str">
+        <x:v>sinopac-tuition-payment-rebate-2026h1</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="str">
+        <x:v>dawho-cashback-card</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>永豐信用卡活動；DAWHO卡適用，依排除卡別規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A15" s="18" t="str">
+        <x:v>sinopac-tuition-payment-rebate-2026h1</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="str">
+        <x:v>sinopac-dual-currency-card</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>永豐信用卡活動；幣倍卡適用，依排除卡別規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A16" s="18" t="str">
+        <x:v>sinopac-utilities-autopay-2percent-2026h2</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="str">
+        <x:v>dawho-cashback-card</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>永豐信用卡活動；DAWHO卡適用，依排除卡別規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A17" s="18" t="str">
+        <x:v>sinopac-utilities-autopay-2percent-2026h2</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="str">
+        <x:v>sinopac-dual-currency-card</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>永豐信用卡活動；幣倍卡適用，依排除卡別規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>ubot-green-card-utilities-autopay-2026h2</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>ubot-green-card</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>聯邦綠卡專屬生活代扣繳1%活動。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>taishin-tuition-installment-2026h2</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>taishin-richart-card</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>全體台新信用卡活動；台新Richart卡適用，依官方排除規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>taishin-tuition-installment-2026h2</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>taishin-jkopay-card</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>全體台新信用卡活動；街口聯名卡適用，依官方排除規定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>taishin-jkopay-card-bill-payments-2026</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>taishin-jkopay-card</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>街口聯名卡專屬街口APP繳稅費／學雜費活動。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
+++ b/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
@@ -953,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.8799991607666" customWidth="1" min="1" max="1"/>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>2026-01-01 至 06-30 以 Paytax 或大咖 DACARD 繳牌照稅、房屋稅、地價稅，單筆滿 NT$3,000 登錄享 6 期 0 利率</t>
+          <t>2026-07-01 至 12-31 以 Paytax 或大咖 DACARD 繳牌照稅、房屋稅、地價稅，單筆滿 NT$3,000 登錄享 6 期 0 利率</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>2026-01-01 至 06-30，持永豐信用卡透過 Paytax 繳稅服務網（網路、QR Code 或中華電信語音）或大咖 DACARD APP 繳納牌照稅、房屋稅、地價稅；正卡持卡人完成分期總約簽署並於登錄當月繳納單筆滿 NT$3,000，登錄後可享 6 期 0 利率。指定稅款同時提供免手續費；活動另有符合歷史代繳條件者的 0.2% 刷卡金方案。</t>
+          <t>2026-07-01 至 12-31，持永豐信用卡透過 Paytax 繳稅服務網（網路、QR Code 或中華電信語音）或大咖 DACARD APP 繳納牌照稅、房屋稅、地價稅；正卡持卡人完成分期總約簽署並於登錄當月繳納單筆滿 NT$3,000，登錄後可享 6 期 0 利率。指定稅款同時提供免手續費；活動另有符合歷史代繳條件者的 0.2% 刷卡金方案。</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K12" s="18" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Q12" s="18" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R12" s="18" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>2026-01-01 至 06-30 透過 i 繳費或學費通繳學費並登錄，當月每滿 NT$50,000 回饋 NT$50，最高 NT$500</t>
+          <t>2026-07-01 至 12-31 透過 i 繳費或學費通繳學費並登錄，當月每滿 NT$50,000 回饋 NT$50，最高 NT$500</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>2026-01-01 至 06-30，透過 i 繳費或聯合信用卡中心學費通平台使用永豐信用卡繳納學費，於繳費當月完成活動登錄後，正附卡合併的當月學費每滿 NT$50,000 回饋 NT$50 刷卡金，每戶每月最高 NT$500；回饋於代繳成功次次月起入帳。另可依單筆分期活動申請 0 利率分期。</t>
+          <t>2026-07-01 至 12-31，透過 i 繳費或聯合信用卡中心學費通平台使用永豐信用卡繳納學費，於繳費當月完成活動登錄後，正附卡合併的當月學費每滿 NT$50,000 回饋 NT$50 刷卡金，每戶每月最高 NT$500；回饋於代繳成功次次月起入帳。另可依單筆分期活動申請 0 利率分期。</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Q13" s="18" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R13" s="18" t="inlineStr">

--- a/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
+++ b/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -66,8 +66,13 @@
       <color rgb="FF111827"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFCC0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +87,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE8E6"/>
+        <bgColor rgb="FFFCE8E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,6 +171,7 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -454,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -470,256 +482,270 @@
       <c r="B1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>本版已被取代</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>請改用 信用卡優惠資料整理模板-v3-2026-07-29.xlsx（搭配 DATA_COLLECTION_SPEC v4-2026-07-29.md，cards 工作表新增 5 個選填卡面配色欄位）。本檔保留作歷史紀錄。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>搭配文件</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>docs/data-collection/DATA_COLLECTION_SPEC_信用卡優惠資料蒐集與分類規格書-v2-2026-07-18.md（完整規則以規格書為準）</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-    </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>填寫規則</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>欄位名稱不要修改、不要增刪欄位；補充資訊寫在「備註」欄。</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>紅字標題 = 必填欄位；查不到的欄位留空白，不要填「無」或「N/A」。</t>
+          <t>欄位名稱不要修改、不要增刪欄位；補充資訊寫在「備註」欄。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日期一律 YYYY-MM-DD（例：2026-09-30）。</t>
+          <t>紅字標題 = 必填欄位；查不到的欄位留空白，不要填「無」或「N/A」。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>每列第 2 列（灰色斜體）是範例，交付前請整列刪除。</t>
+          <t>日期一律 YYYY-MM-DD（例：2026-09-30）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>每筆優惠必須附「官方」來源網址；部落格與比較網站只能當線索。</t>
+          <t>每列第 2 列（灰色斜體）是範例，交付前請整列刪除。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>每筆優惠必須附「官方」來源網址；部落格與比較網站只能當線索。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>一筆優惠適用多張卡：offers 只填 1 列，offer_cards 每張卡填 1 列。</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>主分類代碼（offers 工作表，六選一）</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>cashback</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>現金回饋：不限單一消費場景、以回饋%數為主要賣點</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>dining</t>
+          <t>cashback</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>餐飲美食：限定餐廳、外送、餐飲通路</t>
+          <t>現金回饋：不限單一消費場景、以回饋%數為主要賣點</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>dining</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>旅遊交通：旅遊、機票、訂房、機場服務、海外消費</t>
+          <t>餐飲美食：限定餐廳、外送、餐飲通路</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>online-shopping</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>網購電商：限定電商平台或線上消費</t>
+          <t>旅遊交通：旅遊、機票、訂房、機場服務、海外消費</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>online-shopping</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>交通通勤：加油、停車、大眾運輸、悠遊卡自動加值</t>
+          <t>網購電商：限定電商平台或線上消費</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>交通通勤：加油、停車、大眾運輸、悠遊卡自動加值</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>installment</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>分期零利率：以分期付款、零利率為主要賣點</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>分類判斷順序</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>1.限定場景優先於回饋形式 2.不限場景的回饋→cashback 3.分期優先於場景 4.出遊性質→travel、日常通勤→transport 5.無法判斷→選最接近並在備註寫「分類待確認」</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>回饋類型（offers 工作表，五選一）</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>現金回饋 / 點數回饋 / 折扣 / 分期 / 其他</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>建議標籤用詞</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>新戶、行動支付、海外、加碼、需登錄、長期權益、期間限定、指定通路、繳稅、學費、水電瓦斯、保費、加油、外送、超市量販、旅遊訂房（逗號分隔，用詞統一）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>情境標籤規則（v2 新增）</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>繳稅、學費、水電瓦斯、保費、加油、外送、超市量販、旅遊訂房：官網明確寫適用（或有專屬加碼）才加；官網寫排除就不要加，並在「條件與限制」寫明排除項目。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>cards 新欄位（v2 新增）</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>年費／免年費條件／卡片等級／發卡組織／優點／注意事項皆選填。「優點」「注意事項」在同一儲存格內一行一項（Excel 按 Alt+Enter 換行），只寫官網可查證的事實，不寫主觀評價。</t>
         </is>

--- a/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
+++ b/docs/data-collection/信用卡優惠資料整理模板-v2-2026-07-18.xlsx
@@ -725,7 +725,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
@@ -738,7 +737,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
@@ -2157,7 +2155,7 @@
       </c>
       <c r="R4" s="18" t="inlineStr">
         <is>
-          <t>點數回饋,長期權益,指定通路,行動支付,旅遊訂房,外送,超市量販</t>
+          <t>點數回饋,長期權益,指定通路,行動支付,旅遊訂房,外送,超市量販,訂閱服務</t>
         </is>
       </c>
       <c r="S4" s="18" t="n"/>
